--- a/templates/sample_import_template.xlsx
+++ b/templates/sample_import_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ROG\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ROG\Desktop\TestChamberV7\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36AB49F-620E-461A-8BF0-EE15A326201F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD12C0D-CD3B-43E2-A963-F4078729EE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1150" yWindow="6190" windowWidth="23340" windowHeight="11170" xr2:uid="{91736DB8-3AE9-48DD-8093-FF37CAA71CF4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="样机批量导入模板" sheetId="1" r:id="rId1"/>
@@ -25,16 +25,13 @@
     <author>ROG</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{DD975895-6DA3-4C9B-8858-F33094154D68}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="等线"/>
           </rPr>
           <t>SN/IMEI/主板SN三者必须至少有其一</t>
         </r>
@@ -45,389 +42,263 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+  <si>
+    <t>SN号 *</t>
+  </si>
+  <si>
+    <t>IMEI号 *</t>
+  </si>
+  <si>
+    <t>主板SN *</t>
+  </si>
+  <si>
+    <t>是否重组样机</t>
+  </si>
   <si>
     <t>阶段</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>方案(制式/配置/型号/SKU/厂家)</t>
+  </si>
+  <si>
+    <t>方案编号</t>
+  </si>
+  <si>
+    <t>初检问题录入（无问题不填写或写“/”）</t>
+  </si>
+  <si>
+    <t>挂账人</t>
+  </si>
+  <si>
+    <t>带入位置</t>
+  </si>
+  <si>
+    <t>其他备注信息</t>
+  </si>
+  <si>
+    <t>435872305A0000012</t>
   </si>
   <si>
     <t>86123123123012</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>方案编号</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他备注信息</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>V3-1</t>
+  </si>
+  <si>
+    <t>如: 厂家名称</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>陈十/00123456</t>
+  </si>
+  <si>
+    <t>溪村-DB-B1F-A08</t>
+  </si>
+  <si>
+    <t>435872305A0000013</t>
+  </si>
+  <si>
+    <t>012312312312312313</t>
+  </si>
+  <si>
+    <t>如: 方案缩写 BOE</t>
+  </si>
+  <si>
+    <t>有异响</t>
+  </si>
+  <si>
+    <t>李八/wx1234567</t>
+  </si>
+  <si>
+    <t>435872305A0000014</t>
   </si>
   <si>
     <t>86567567567056</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>方案(制式/配置/型号/SKU/厂家)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">主板SN </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">SN号 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">IMEI号 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>012312312312312312</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>012312312312312313</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>挂账人</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>V3-1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>带入位置</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>初检问题录入</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（无问题不填写或写“/”）</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>435872305A0000012</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>435872305A0000013</t>
-  </si>
-  <si>
-    <t>435872305A0000014</t>
-  </si>
-  <si>
-    <t>如: 厂家名称</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>A1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>陈十/00123456</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>如: 方案缩写 BOE</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>有异响</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>李八/wx1234567</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>如：来源名称</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-1</t>
   </si>
   <si>
     <t>/</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>赵六/324234324</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2-1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>溪村-DB-B1F-A08</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>012312312312312166</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
       <name val="等线 Light"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+    </font>
+    <font>
       <sz val="9"/>
-      <color indexed="81"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="10"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -476,13 +347,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.79995117038483843"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59996337778862885"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -499,13 +370,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.79995117038483843"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59996337778862885"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -522,13 +393,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.79995117038483843"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59996337778862885"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -545,13 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.79995117038483843"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59996337778862885"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -568,13 +439,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.79995117038483843"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59996337778862885"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -591,13 +462,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.79995117038483843"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59996337778862885"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -610,12 +481,28 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -642,7 +529,7 @@
       <right/>
       <top/>
       <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49995422223578601"/>
       </bottom>
       <diagonal/>
     </border>
@@ -879,80 +766,102 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="20" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="23" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 1" xfId="19" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="20% - 着色 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - 着色 3" xfId="27" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="20% - 着色 4" xfId="31" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - 着色 5" xfId="35" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% - 着色 6" xfId="39" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="40% - 着色 1" xfId="20" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="40% - 着色 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="40% - 着色 3" xfId="28" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="40% - 着色 4" xfId="32" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="40% - 着色 5" xfId="36" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="40% - 着色 6" xfId="40" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="60% - 着色 1" xfId="21" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="60% - 着色 2" xfId="25" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="60% - 着色 3" xfId="29" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="60% - 着色 4" xfId="33" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="60% - 着色 5" xfId="37" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="60% - 着色 6" xfId="41" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="标题" xfId="1" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="标题 1" xfId="2" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="标题 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="标题 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="标题 4" xfId="5" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="差" xfId="7" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="好" xfId="6" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="汇总" xfId="17" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="计算" xfId="11" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="检查单元格" xfId="13" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="解释性文本" xfId="16" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="警告文本" xfId="14" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="链接单元格" xfId="12" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="适中" xfId="8" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="输出" xfId="10" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="输入" xfId="9" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="着色 1" xfId="18" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="着色 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="着色 3" xfId="26" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="着色 4" xfId="30" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="着色 5" xfId="34" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="着色 6" xfId="38" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="注释" xfId="15" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFFFFFFF"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -964,8 +873,116 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1026" name="Text Box 2" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{412F1D74-83BA-0DFC-38DA-5F9D5CDF0CFE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noSelect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6350000" cy="6350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40E6FC0F-E2C1-C2B4-627A-62DC3E58689A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6826250" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1007,108 +1024,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1116,80 +1039,31 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1219,22 +1093,22 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1251,157 +1125,254 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176E7DEF-E4B2-4008-90AA-83D5D5B61F1A}">
-  <dimension ref="A1:J5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="21.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="11.25" style="3" customWidth="1"/>
-    <col min="5" max="5" width="31.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="38" style="3" customWidth="1"/>
-    <col min="8" max="8" width="19.9140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="24.5" style="3" customWidth="1"/>
-    <col min="10" max="10" width="19" style="6" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.9140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="13"/>
+      <c r="D2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="4" t="s">
+      <c r="F2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="13"/>
+    </row>
+    <row r="3" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="13"/>
+    </row>
+    <row r="4" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="13"/>
+    </row>
+    <row r="5" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="E5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="13"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="3"/>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="14"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="3"/>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="14"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="3"/>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="14"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>25</v>
-      </c>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="14"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="14"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="14"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>